--- a/Reporte_Eventos_Seguridad.xlsx
+++ b/Reporte_Eventos_Seguridad.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,1414 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EVT-AED62891E64A4EA597365EE94990F37C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>14:23:15.441</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_142315_436_4990F37C.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EVT-4D2FDA81163647A59CE04BA28BBABACF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>14:23:15.754</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_142315_754_8BBABACF.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EVT-ED05E274ADFD40BAA2C4F2366BC159C3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>14:24:14.449</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_142414_433_6BC159C3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EVT-9562B71FC5CB4EE1AB539CADC96F5FA2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>14:24:17.283</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_142417_268_C96F5FA2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EVT-7CB73F3492AA45FBBEE7333F4D8D510E</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>14:30:07.793</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143007_793_4D8D510E.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EVT-AD26EBC539EA4F17B879EB15573E1369</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>14:30:56.015</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143056_015_573E1369.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EVT-7F53A32EF2894CE3BB1DF62984E59881</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>14:31:09.157</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143109_157_84E59881.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EVT-D830EF2C1DB844E0A2C1DBF1B9CB7CA2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>14:31:42.789</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143142_789_B9CB7CA2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EVT-E53AFFDD52BE4C5DAB8BEBF02D03CD4C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>14:32:15.841</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143215_837_2D03CD4C.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EVT-BE060CA38EF14AB5A13706226672332D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>14:32:19.680</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143219_680_6672332D.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EVT-12F09BCD14494E4B9127F64A1EB7040D</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>14:32:23.426</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143223_426_1EB7040D.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EVT-3AAB0E555CCF452886CDD842D84C7A48</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>14:32:47.596</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143247_592_D84C7A48.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EVT-9419A0F240A1424EAD6C17EDE31449C9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>14:32:48.742</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143248_734_E31449C9.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EVT-A62C655C94624253AD9058034C2A3E1B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>14:32:52.323</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>POSIBLE_CAIDA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_POSIBLE_CAIDA_20260724_143252_323_4C2A3E1B.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EVT-7FF806AA430B4D35ADE852D50814AC86</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>14:32:52.745</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143252_740_0814AC86.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EVT-16B2E071222243CA95E66D1550820F92</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>14:33:20.705</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143320_689_50820F92.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EVT-43A4EA9D4A784AB7AD79B8A993813F8D</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>14:34:21.865</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143421_865_93813F8D.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EVT-2ACFCD1C20F94C1C8525B848A4EA57F9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>14:34:23.314</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143423_299_A4EA57F9.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EVT-598EB4CF8ACE469A8393CE4D5D57DF14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14:35:07.673</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143507_673_5D57DF14.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EVT-A22B641A9AA74B2C91F20569003072FC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>14:35:09.324</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143509_324_003072FC.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EVT-1BA332B2149B4CFDAABDC0BFD6CA5F71</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>14:35:09.340</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>POSIBLE_CAIDA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_POSIBLE_CAIDA_20260724_143509_324_D6CA5F71.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EVT-95AEDF5C8EAE4519B8AD2AD97E919E7F</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CAM_PUERTA01_ADM_CONCENTRADORA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>14:38:36.868</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_PUERTA01_ADM_CONCENTRADORA_INCUMPLIMIENTO_EPP_20260724_143836_866_7E919E7F.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reporte_Eventos_Seguridad.xlsx
+++ b/Reporte_Eventos_Seguridad.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2216,6 +2216,3462 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EVT-10600F035BAF40349EEF4E8D674D1B43</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>15:01:18.219</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_150118_214_674D1B43.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EVT-21D82F190D174B548BA4AADEDF635DFE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>15:01:22.122</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_150122_119_DF635DFE.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EVT-395742AE89F64132B359C951B8DC1D7F</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>15:01:25.050</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_150125_046_B8DC1D7F.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EVT-290EC57AF5DA4EC7B420DDDC648888A8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>15:14:59.790</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_151459_783_648888A8.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EVT-654724D9D8AB4655A0F6AA6785C2C539</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>15:15:01.110</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_151501_100_85C2C539.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EVT-37EB757A6DF944008CCE4D4275E89B8D</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>15:15:05.050</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_151505_041_75E89B8D.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EVT-6A16CD335B734BB7BA75BEA96C639DA7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>15:17:54.649</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_151754_642_6C639DA7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EVT-46AFD9D4A70844B897F51FAB8D38B65A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>15:18:23.129</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_151823_124_8D38B65A.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EVT-069EEE620D514F069A235A09A783B800</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>15:20:52.428</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_152052_420_A783B800.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EVT-6C5157A8BCD94811A7D1D2869D8D7DDD</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>15:26:25.716</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_152625_706_9D8D7DDD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EVT-2656D44F0BDF485D96B0E16FBCDF2D8A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>15:28:36.475</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_152836_468_BCDF2D8A.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EVT-D2FECD648CB64D36A3D54900018F0E78</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>15:29:00.545</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_152900_545_018F0E78.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EVT-3D45301A4CB4410695FD03219857BE1C</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>15:29:01.625</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_152901_625_9857BE1C.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EVT-F1A63859AB0D47418AE542657F323406</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>15:31:55.759</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153155_754_7F323406.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EVT-09C976D0D5424FEDA76EE04665FC2F00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>15:31:58.549</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153158_544_65FC2F00.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EVT-21F2B68DEA9644A48197A7831417ED56</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>15:32:15.423</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153215_423_1417ED56.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EVT-8A5ED6DDD0E14CB6B24320A8A388A8C7</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>15:32:17.921</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153217_913_A388A8C7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EVT-ADD6664CDE00424D9C231C7A0BE370CF</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>15:32:19.125</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153219_113_0BE370CF.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EVT-5D0194F62C9C4157B13C9A418DB50ACE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>15:33:37.543</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153337_542_8DB50ACE.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EVT-88685B79EF914BCEB46BF61B3463BF0E</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>15:34:09.582</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153409_582_3463BF0E.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EVT-30AD28349C2B4DBBB66176ED24DF2D09</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>15:34:12.628</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153412_622_24DF2D09.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EVT-8D173F7DD9654471867859E19B5DE043</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>15:34:45.940</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153445_932_9B5DE043.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EVT-B6BEC2CF14A249059FE0DC15A0AF0444</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>15:35:07.944</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153507_944_A0AF0444.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EVT-74DEB72F067041E78243DB7EB5CCF681</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>15:35:10.681</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_153510_668_B5CCF681.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EVT-511A359727A64BE1B886178394A87BD7</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>15:48:02.668</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_154802_658_94A87BD7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EVT-ABF20AF56D6E4D599E1D9683705F0472</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>15:48:35.898</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_154835_891_705F0472.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EVT-773DF7BB39014AD4A76D45161A38702F</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>15:48:53.978</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_154853_968_1A38702F.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EVT-C33DE6988288488DB84D5B66C3511E3F</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>15:48:59.518</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_154859_515_C3511E3F.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EVT-6B64C59941C04D07A9ABE3F1E6AFED24</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>15:49:00.558</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_154900_558_E6AFED24.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EVT-8DD9F1690FEA489DA89355EA8BA96A1E</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>15:49:01.742</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_154901_737_8BA96A1E.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EVT-528EA3B662114984988063973FA61461</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>15:49:04.140</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_154904_140_3FA61461.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EVT-3FACE20FA5204E8E9D3F60FD9089E93E</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>15:50:25.203</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155025_188_9089E93E.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EVT-42449F61E196476A83D84E220C0F0521</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>15:50:31.573</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155031_563_0C0F0521.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EVT-C8C25D1C8058451686575FA2FAFEB8E8</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>15:50:32.739</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155032_738_FAFEB8E8.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EVT-7A1B5DB006E94F5581D36367EDDD656B</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>15:52:22.967</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155222_957_EDDD656B.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EVT-4B8BB95BAC6B499A958A9DD382B004EC</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>15:53:26.557</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155326_548_82B004EC.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EVT-049BB3C7D3F849D6A74E9539E9AB25F9</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>15:53:26.891</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155326_877_E9AB25F9.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EVT-48D4BFC40153462CBC0DF6949FD3275C</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>15:53:27.017</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155327_009_9FD3275C.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EVT-A7CF3CD2949441F38D3FF5C4203887E1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>15:54:05.867</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155405_860_203887E1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EVT-FE6C5D4D81304F1088AB1BD07B7D051C</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>15:54:14.049</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155414_037_7B7D051C.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EVT-2E2E36875DAA434CA69E38DA7FBF1C66</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>15:58:16.065</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155816_055_7FBF1C66.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EVT-47BF1C75E973496EB83CEBA28F7FA152</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>15:59:25.009</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_155925_004_8F7FA152.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EVT-75CAE8F3EC134903BBEAFC1A3AA1F173</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>16:28:04.677</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162804_669_3AA1F173.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EVT-4E60F564D1534728BC88FA89FED580A0</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>16:28:06.391</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162806_337_FED580A0.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EVT-ADCC1E7E2EF64260A036D6DB0F70CC39</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>16:28:13.211</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162813_203_0F70CC39.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EVT-BED2A86586444D1384BDF9F9E25611E7</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>16:28:14.315</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162814_306_E25611E7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EVT-917669DC7D2A40FAB033784BE80D26B0</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>16:28:16.830</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162816_824_E80D26B0.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EVT-D0EADB9B836140A5AC346003D03FF809</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>16:28:23.855</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162823_847_D03FF809.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EVT-B7F29F5E375F41E984E69EE529415B52</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>16:28:28.173</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162828_167_29415B52.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EVT-D6A9C84613ED43A6B590855015E681E9</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>16:28:29.085</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162829_076_15E681E9.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EVT-40B02F0F2AD443358891746234417141</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>16:28:47.983</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162847_975_34417141.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EVT-F3288197B66E46D0B518F95277484EE6</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>16:28:48.185</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162848_169_77484EE6.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EVT-A391BBDF11874299B192B265B36D4344</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>16:28:53.423</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162853_413_B36D4344.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EVT-3EE2D66CC7F842969C02AB9740084928</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CAM_P01_ADM</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>16:29:12.550</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>INCUMPLIMIENTO_EPP</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sin Casco y Chaleco</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Evidencias\CAM_P01_ADM_INCUMPLIMIENTO_EPP_20260724_162912_503_40084928.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reporte_Eventos_Seguridad.xlsx
+++ b/Reporte_Eventos_Seguridad.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Evento_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Camara</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Tipo_Evento</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Casco</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Chaleco</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Estado_EPP</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confianza_Evento</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ID_Seguimiento_Temporal</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Estado_Revision</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Identificacion_Humana</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Observaciones_Revision</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Foto</t>
         </is>
